--- a/plc/s7-1x00/core/motion-control/EMotionControlCommands-v1.1.xlsx
+++ b/plc/s7-1x00/core/motion-control/EMotionControlCommands-v1.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\motion-control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9679EA52-7657-4F7D-B6C8-10CD434E0C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AB84C2-4CED-4EBB-99EF-434A206C1AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -132,13 +132,22 @@
   </si>
   <si>
     <t>MC_CMD_10_PROFILE_TABLE</t>
+  </si>
+  <si>
+    <t>Bool</t>
+  </si>
+  <si>
+    <t>EMotionControlCommands</t>
+  </si>
+  <si>
+    <t>{"version":"v1.1","author":"cyanezf","family":"core/motion-control","status":"current","deprecatedBy":null,"dependencies":[]}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -480,13 +489,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,238 +512,255 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
         <v>31</v>
       </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
         <v>33</v>
       </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15">
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
         <v>10</v>
       </c>
     </row>
@@ -746,9 +772,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -759,7 +785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
